--- a/dados/orcamentos_tematicos/crianca_adolescente/OCA_QUADRIMESTRE/2018/Relatório do OCA 3o quad 2018.xlsx
+++ b/dados/orcamentos_tematicos/crianca_adolescente/OCA_QUADRIMESTRE/2018/Relatório do OCA 3o quad 2018.xlsx
@@ -1,20 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backup\D\Denise\Gerência PPAG atual\Docs 2019\Audiência 3o quadrimestre 2018\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\pbh_visualizacao_de_dados\dados\orcamentos_tematicos\crianca_adolescente\OCA_QUADRIMESTRE\2018\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46697402-B20E-4040-9087-1DAC6FD7ACD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="6555"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Relatório do OCA 2018" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1641,7 +1656,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2004,14 +2019,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T409"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="256" width="12.7109375" customWidth="1"/>
+    <col min="1" max="256" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>538</v>
       </c>
@@ -2035,7 +2050,7 @@
       <c r="S1" s="6"/>
       <c r="T1" s="6"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>528</v>
       </c>
@@ -2097,7 +2112,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2159,7 +2174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -2221,7 +2236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
@@ -2283,7 +2298,7 @@
         <v>204245.75</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -2345,7 +2360,7 @@
         <v>3037.5</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
@@ -2407,7 +2422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>0</v>
       </c>
@@ -2469,7 +2484,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>0</v>
       </c>
@@ -2531,7 +2546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>0</v>
       </c>
@@ -2593,7 +2608,7 @@
         <v>13557.452499999999</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -2655,7 +2670,7 @@
         <v>619387.58250000002</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>0</v>
       </c>
@@ -2717,7 +2732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
@@ -2779,7 +2794,7 @@
         <v>33641.517500000002</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>0</v>
       </c>
@@ -2841,7 +2856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>0</v>
       </c>
@@ -2903,7 +2918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>0</v>
       </c>
@@ -2965,7 +2980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>0</v>
       </c>
@@ -3027,7 +3042,7 @@
         <v>5903818.8449999997</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>0</v>
       </c>
@@ -3089,7 +3104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>0</v>
       </c>
@@ -3151,7 +3166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -3213,7 +3228,7 @@
         <v>127222.9375</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>0</v>
       </c>
@@ -3275,7 +3290,7 @@
         <v>750024.55249999999</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>0</v>
       </c>
@@ -3337,7 +3352,7 @@
         <v>17994.837500000001</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>0</v>
       </c>
@@ -3399,7 +3414,7 @@
         <v>22750</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>0</v>
       </c>
@@ -3461,7 +3476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>0</v>
       </c>
@@ -3523,7 +3538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>0</v>
       </c>
@@ -3585,7 +3600,7 @@
         <v>531754.59750000003</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>0</v>
       </c>
@@ -3647,7 +3662,7 @@
         <v>964006.31499999994</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>0</v>
       </c>
@@ -3709,7 +3724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>0</v>
       </c>
@@ -3771,7 +3786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>0</v>
       </c>
@@ -3833,7 +3848,7 @@
         <v>12099.372499999999</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>0</v>
       </c>
@@ -3895,7 +3910,7 @@
         <v>1828683.2150000001</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>0</v>
       </c>
@@ -3957,7 +3972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>0</v>
       </c>
@@ -4019,7 +4034,7 @@
         <v>1300919.0725</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>0</v>
       </c>
@@ -4081,7 +4096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>0</v>
       </c>
@@ -4143,7 +4158,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>0</v>
       </c>
@@ -4205,7 +4220,7 @@
         <v>50195.75</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>0</v>
       </c>
@@ -4267,7 +4282,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>0</v>
       </c>
@@ -4329,7 +4344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>0</v>
       </c>
@@ -4391,7 +4406,7 @@
         <v>9363.0949999999993</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>0</v>
       </c>
@@ -4453,7 +4468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>0</v>
       </c>
@@ -4515,7 +4530,7 @@
         <v>65922.824999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>0</v>
       </c>
@@ -4577,7 +4592,7 @@
         <v>86546.012499999997</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>0</v>
       </c>
@@ -4639,7 +4654,7 @@
         <v>6100.04</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>0</v>
       </c>
@@ -4701,7 +4716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>0</v>
       </c>
@@ -4763,7 +4778,7 @@
         <v>95549.8</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>0</v>
       </c>
@@ -4825,7 +4840,7 @@
         <v>46553.995000000003</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>0</v>
       </c>
@@ -4887,7 +4902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>0</v>
       </c>
@@ -4949,7 +4964,7 @@
         <v>149625</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>0</v>
       </c>
@@ -5011,7 +5026,7 @@
         <v>1353040.4750000001</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>0</v>
       </c>
@@ -5073,7 +5088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>0</v>
       </c>
@@ -5135,7 +5150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>0</v>
       </c>
@@ -5197,7 +5212,7 @@
         <v>385995.4</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>0</v>
       </c>
@@ -5259,7 +5274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>0</v>
       </c>
@@ -5321,7 +5336,7 @@
         <v>33110.65</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>0</v>
       </c>
@@ -5383,7 +5398,7 @@
         <v>939814.3125</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>0</v>
       </c>
@@ -5445,7 +5460,7 @@
         <v>1209.7325000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>0</v>
       </c>
@@ -5507,7 +5522,7 @@
         <v>9769.0249999999996</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>0</v>
       </c>
@@ -5569,7 +5584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>0</v>
       </c>
@@ -5631,7 +5646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>0</v>
       </c>
@@ -5693,7 +5708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>0</v>
       </c>
@@ -5755,7 +5770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>0</v>
       </c>
@@ -5817,7 +5832,7 @@
         <v>214205</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>0</v>
       </c>
@@ -5879,7 +5894,7 @@
         <v>22502.255000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>0</v>
       </c>
@@ -5941,7 +5956,7 @@
         <v>1232163.6675</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>0</v>
       </c>
@@ -6003,7 +6018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>0</v>
       </c>
@@ -6065,7 +6080,7 @@
         <v>1743.7149999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>0</v>
       </c>
@@ -6127,7 +6142,7 @@
         <v>751289.47250000003</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>0</v>
       </c>
@@ -6189,7 +6204,7 @@
         <v>50737.902499999997</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>0</v>
       </c>
@@ -6251,7 +6266,7 @@
         <v>47846.037499999999</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>0</v>
       </c>
@@ -6313,7 +6328,7 @@
         <v>20234.172500000001</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>0</v>
       </c>
@@ -6375,7 +6390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>0</v>
       </c>
@@ -6437,7 +6452,7 @@
         <v>3059.4</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>0</v>
       </c>
@@ -6499,7 +6514,7 @@
         <v>478.85</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>0</v>
       </c>
@@ -6561,7 +6576,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>0</v>
       </c>
@@ -6623,7 +6638,7 @@
         <v>6543688.4199999999</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>0</v>
       </c>
@@ -6685,7 +6700,7 @@
         <v>6426532</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>0</v>
       </c>
@@ -6747,7 +6762,7 @@
         <v>7147201.9199999999</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>0</v>
       </c>
@@ -6809,7 +6824,7 @@
         <v>218364.4675</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>0</v>
       </c>
@@ -6871,7 +6886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>0</v>
       </c>
@@ -6933,7 +6948,7 @@
         <v>6865523.2699999996</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>0</v>
       </c>
@@ -6995,7 +7010,7 @@
         <v>2803728.72</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>0</v>
       </c>
@@ -7057,7 +7072,7 @@
         <v>805892.63</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>0</v>
       </c>
@@ -7119,7 +7134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>0</v>
       </c>
@@ -7181,7 +7196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>0</v>
       </c>
@@ -7243,7 +7258,7 @@
         <v>31977.866999999998</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>0</v>
       </c>
@@ -7305,7 +7320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>0</v>
       </c>
@@ -7367,7 +7382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>0</v>
       </c>
@@ -7429,7 +7444,7 @@
         <v>7393.8975</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>0</v>
       </c>
@@ -7491,7 +7506,7 @@
         <v>3478</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>0</v>
       </c>
@@ -7553,7 +7568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>0</v>
       </c>
@@ -7615,7 +7630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>0</v>
       </c>
@@ -7677,7 +7692,7 @@
         <v>151889994.41</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>0</v>
       </c>
@@ -7739,7 +7754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>0</v>
       </c>
@@ -7801,7 +7816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>0</v>
       </c>
@@ -7863,7 +7878,7 @@
         <v>904311.72</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>0</v>
       </c>
@@ -7925,7 +7940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>0</v>
       </c>
@@ -7987,7 +8002,7 @@
         <v>6561</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>0</v>
       </c>
@@ -8049,7 +8064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>0</v>
       </c>
@@ -8111,7 +8126,7 @@
         <v>295445.96999999997</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>0</v>
       </c>
@@ -8173,7 +8188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>0</v>
       </c>
@@ -8235,7 +8250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>0</v>
       </c>
@@ -8297,7 +8312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>0</v>
       </c>
@@ -8359,7 +8374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>0</v>
       </c>
@@ -8421,7 +8436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>0</v>
       </c>
@@ -8483,7 +8498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>0</v>
       </c>
@@ -8545,7 +8560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>0</v>
       </c>
@@ -8607,7 +8622,7 @@
         <v>3645007.34</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>0</v>
       </c>
@@ -8669,7 +8684,7 @@
         <v>1429199.21</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>0</v>
       </c>
@@ -8731,7 +8746,7 @@
         <v>48332800.609999999</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>0</v>
       </c>
@@ -8793,7 +8808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>0</v>
       </c>
@@ -8855,7 +8870,7 @@
         <v>30358645.940000001</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>0</v>
       </c>
@@ -8917,7 +8932,7 @@
         <v>96160699.069999993</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>0</v>
       </c>
@@ -8979,7 +8994,7 @@
         <v>2042341</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>0</v>
       </c>
@@ -9041,7 +9056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>0</v>
       </c>
@@ -9103,7 +9118,7 @@
         <v>737670249.35000002</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>0</v>
       </c>
@@ -9165,7 +9180,7 @@
         <v>5166260.95</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>0</v>
       </c>
@@ -9227,7 +9242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>0</v>
       </c>
@@ -9289,7 +9304,7 @@
         <v>10453789.199999999</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>0</v>
       </c>
@@ -9351,7 +9366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>0</v>
       </c>
@@ -9413,7 +9428,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>0</v>
       </c>
@@ -9475,7 +9490,7 @@
         <v>6287.86</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>0</v>
       </c>
@@ -9537,7 +9552,7 @@
         <v>4896780</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>0</v>
       </c>
@@ -9599,7 +9614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>0</v>
       </c>
@@ -9661,7 +9676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>0</v>
       </c>
@@ -9723,7 +9738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>0</v>
       </c>
@@ -9785,7 +9800,7 @@
         <v>2608570.58</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>0</v>
       </c>
@@ -9847,7 +9862,7 @@
         <v>3119670.3</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>0</v>
       </c>
@@ -9909,7 +9924,7 @@
         <v>7784.26</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>0</v>
       </c>
@@ -9971,7 +9986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>0</v>
       </c>
@@ -10033,7 +10048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>0</v>
       </c>
@@ -10095,7 +10110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>0</v>
       </c>
@@ -10157,7 +10172,7 @@
         <v>2569225.5699999998</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>0</v>
       </c>
@@ -10219,7 +10234,7 @@
         <v>437596.48</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>0</v>
       </c>
@@ -10281,7 +10296,7 @@
         <v>10609712.859999999</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>0</v>
       </c>
@@ -10343,7 +10358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>0</v>
       </c>
@@ -10405,7 +10420,7 @@
         <v>3871138.72</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>0</v>
       </c>
@@ -10467,7 +10482,7 @@
         <v>4605169.3499999996</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>0</v>
       </c>
@@ -10529,7 +10544,7 @@
         <v>66549</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>0</v>
       </c>
@@ -10591,7 +10606,7 @@
         <v>322040974.16000003</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>0</v>
       </c>
@@ -10653,7 +10668,7 @@
         <v>161792146.06</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>0</v>
       </c>
@@ -10715,7 +10730,7 @@
         <v>1828073.21</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>0</v>
       </c>
@@ -10777,7 +10792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>0</v>
       </c>
@@ -10839,7 +10854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>0</v>
       </c>
@@ -10901,7 +10916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>0</v>
       </c>
@@ -10963,7 +10978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>0</v>
       </c>
@@ -11025,7 +11040,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>0</v>
       </c>
@@ -11087,7 +11102,7 @@
         <v>52261.125</v>
       </c>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>0</v>
       </c>
@@ -11149,7 +11164,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>0</v>
       </c>
@@ -11211,7 +11226,7 @@
         <v>4504454.2249999996</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>0</v>
       </c>
@@ -11273,7 +11288,7 @@
         <v>98048.2</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>0</v>
       </c>
@@ -11335,7 +11350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>0</v>
       </c>
@@ -11397,7 +11412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>0</v>
       </c>
@@ -11459,7 +11474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>0</v>
       </c>
@@ -11521,7 +11536,7 @@
         <v>62250</v>
       </c>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>0</v>
       </c>
@@ -11583,7 +11598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>0</v>
       </c>
@@ -11645,7 +11660,7 @@
         <v>153334.6</v>
       </c>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>0</v>
       </c>
@@ -11707,7 +11722,7 @@
         <v>742305.5</v>
       </c>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>0</v>
       </c>
@@ -11769,7 +11784,7 @@
         <v>2964</v>
       </c>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>0</v>
       </c>
@@ -11831,7 +11846,7 @@
         <v>79108.429999999993</v>
       </c>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>0</v>
       </c>
@@ -11893,7 +11908,7 @@
         <v>6276888.6299999999</v>
       </c>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>0</v>
       </c>
@@ -11955,7 +11970,7 @@
         <v>330000</v>
       </c>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>0</v>
       </c>
@@ -12017,7 +12032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>0</v>
       </c>
@@ -12079,7 +12094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>0</v>
       </c>
@@ -12141,7 +12156,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>0</v>
       </c>
@@ -12203,7 +12218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>0</v>
       </c>
@@ -12265,7 +12280,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>0</v>
       </c>
@@ -12327,7 +12342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>0</v>
       </c>
@@ -12389,7 +12404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>0</v>
       </c>
@@ -12451,7 +12466,7 @@
         <v>4224.1949999999997</v>
       </c>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>0</v>
       </c>
@@ -12513,7 +12528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>0</v>
       </c>
@@ -12575,7 +12590,7 @@
         <v>28805.967499999999</v>
       </c>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>0</v>
       </c>
@@ -12637,7 +12652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>0</v>
       </c>
@@ -12699,7 +12714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>0</v>
       </c>
@@ -12761,7 +12776,7 @@
         <v>55250</v>
       </c>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>0</v>
       </c>
@@ -12823,7 +12838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>215</v>
       </c>
@@ -12885,7 +12900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>215</v>
       </c>
@@ -12947,7 +12962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>215</v>
       </c>
@@ -13009,7 +13024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>215</v>
       </c>
@@ -13071,7 +13086,7 @@
         <v>622.5</v>
       </c>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>215</v>
       </c>
@@ -13133,7 +13148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>215</v>
       </c>
@@ -13195,7 +13210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>215</v>
       </c>
@@ -13257,7 +13272,7 @@
         <v>9766342.6524999999</v>
       </c>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>215</v>
       </c>
@@ -13319,7 +13334,7 @@
         <v>247672.08</v>
       </c>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>215</v>
       </c>
@@ -13381,7 +13396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>215</v>
       </c>
@@ -13443,7 +13458,7 @@
         <v>495817.1225</v>
       </c>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>215</v>
       </c>
@@ -13505,7 +13520,7 @@
         <v>3150061.49</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>215</v>
       </c>
@@ -13567,7 +13582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>215</v>
       </c>
@@ -13629,7 +13644,7 @@
         <v>23874296.960000001</v>
       </c>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>215</v>
       </c>
@@ -13691,7 +13706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>215</v>
       </c>
@@ -13753,7 +13768,7 @@
         <v>712007.83</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>215</v>
       </c>
@@ -13815,7 +13830,7 @@
         <v>498926.59</v>
       </c>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>215</v>
       </c>
@@ -13877,7 +13892,7 @@
         <v>1530719.96</v>
       </c>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>215</v>
       </c>
@@ -13939,7 +13954,7 @@
         <v>311958</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>215</v>
       </c>
@@ -14001,7 +14016,7 @@
         <v>261479.9</v>
       </c>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>215</v>
       </c>
@@ -14063,7 +14078,7 @@
         <v>1863.86</v>
       </c>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>215</v>
       </c>
@@ -14125,7 +14140,7 @@
         <v>365791.79</v>
       </c>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>215</v>
       </c>
@@ -14187,7 +14202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>215</v>
       </c>
@@ -14249,7 +14264,7 @@
         <v>543.03</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>215</v>
       </c>
@@ -14311,7 +14326,7 @@
         <v>6544.51</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>215</v>
       </c>
@@ -14373,7 +14388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>215</v>
       </c>
@@ -14435,7 +14450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>215</v>
       </c>
@@ -14497,7 +14512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>215</v>
       </c>
@@ -14559,7 +14574,7 @@
         <v>357382.23</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>215</v>
       </c>
@@ -14621,7 +14636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>215</v>
       </c>
@@ -14683,7 +14698,7 @@
         <v>6045936.6200000001</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>215</v>
       </c>
@@ -14745,7 +14760,7 @@
         <v>1450234.7825</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>215</v>
       </c>
@@ -14807,7 +14822,7 @@
         <v>1297011.5275000001</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>215</v>
       </c>
@@ -14869,7 +14884,7 @@
         <v>3343.58</v>
       </c>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>215</v>
       </c>
@@ -14931,7 +14946,7 @@
         <v>235121.315</v>
       </c>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>215</v>
       </c>
@@ -14993,7 +15008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>215</v>
       </c>
@@ -15055,7 +15070,7 @@
         <v>1596.0050000000001</v>
       </c>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>215</v>
       </c>
@@ -15117,7 +15132,7 @@
         <v>4629037.7175000003</v>
       </c>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>215</v>
       </c>
@@ -15179,7 +15194,7 @@
         <v>120276.06</v>
       </c>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>215</v>
       </c>
@@ -15241,7 +15256,7 @@
         <v>216623.36249999999</v>
       </c>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>215</v>
       </c>
@@ -15303,7 +15318,7 @@
         <v>261382.315</v>
       </c>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>215</v>
       </c>
@@ -15365,7 +15380,7 @@
         <v>1003161.3625</v>
       </c>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>215</v>
       </c>
@@ -15427,7 +15442,7 @@
         <v>1027270.49</v>
       </c>
     </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>215</v>
       </c>
@@ -15489,7 +15504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>215</v>
       </c>
@@ -15551,7 +15566,7 @@
         <v>371456.9</v>
       </c>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>215</v>
       </c>
@@ -15613,7 +15628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>215</v>
       </c>
@@ -15675,7 +15690,7 @@
         <v>443010.34</v>
       </c>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>215</v>
       </c>
@@ -15737,7 +15752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>215</v>
       </c>
@@ -15799,7 +15814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>215</v>
       </c>
@@ -15861,7 +15876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>215</v>
       </c>
@@ -15923,7 +15938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>215</v>
       </c>
@@ -15985,7 +16000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>215</v>
       </c>
@@ -16047,7 +16062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>215</v>
       </c>
@@ -16109,7 +16124,7 @@
         <v>45132.14</v>
       </c>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>215</v>
       </c>
@@ -16171,7 +16186,7 @@
         <v>4243054.2249999996</v>
       </c>
     </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>215</v>
       </c>
@@ -16233,7 +16248,7 @@
         <v>959545.97250000003</v>
       </c>
     </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>215</v>
       </c>
@@ -16295,7 +16310,7 @@
         <v>343577.5025</v>
       </c>
     </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>215</v>
       </c>
@@ -16357,7 +16372,7 @@
         <v>1225259.96</v>
       </c>
     </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>215</v>
       </c>
@@ -16419,7 +16434,7 @@
         <v>233820</v>
       </c>
     </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>215</v>
       </c>
@@ -16481,7 +16496,7 @@
         <v>78511.767500000002</v>
       </c>
     </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>215</v>
       </c>
@@ -16543,7 +16558,7 @@
         <v>124.97499999999999</v>
       </c>
     </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>215</v>
       </c>
@@ -16605,7 +16620,7 @@
         <v>653.85</v>
       </c>
     </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>215</v>
       </c>
@@ -16667,7 +16682,7 @@
         <v>39938.375</v>
       </c>
     </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>215</v>
       </c>
@@ -16729,7 +16744,7 @@
         <v>282.14999999999998</v>
       </c>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>215</v>
       </c>
@@ -16791,7 +16806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>215</v>
       </c>
@@ -16853,7 +16868,7 @@
         <v>40342.625</v>
       </c>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>215</v>
       </c>
@@ -16915,7 +16930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>215</v>
       </c>
@@ -16977,7 +16992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>215</v>
       </c>
@@ -17039,7 +17054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>215</v>
       </c>
@@ -17101,7 +17116,7 @@
         <v>17421.57</v>
       </c>
     </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>215</v>
       </c>
@@ -17163,7 +17178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>215</v>
       </c>
@@ -17225,7 +17240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>215</v>
       </c>
@@ -17287,7 +17302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>215</v>
       </c>
@@ -17349,7 +17364,7 @@
         <v>1201.75</v>
       </c>
     </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>215</v>
       </c>
@@ -17411,7 +17426,7 @@
         <v>18435.25</v>
       </c>
     </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>215</v>
       </c>
@@ -17473,7 +17488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>215</v>
       </c>
@@ -17535,7 +17550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>215</v>
       </c>
@@ -17597,7 +17612,7 @@
         <v>1402441.35</v>
       </c>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>215</v>
       </c>
@@ -17659,7 +17674,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>215</v>
       </c>
@@ -17721,7 +17736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>215</v>
       </c>
@@ -17783,7 +17798,7 @@
         <v>2771984.87</v>
       </c>
     </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>215</v>
       </c>
@@ -17845,7 +17860,7 @@
         <v>2106781.31</v>
       </c>
     </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>215</v>
       </c>
@@ -17907,7 +17922,7 @@
         <v>3334.3274999999999</v>
       </c>
     </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>215</v>
       </c>
@@ -17969,7 +17984,7 @@
         <v>8409.6625000000004</v>
       </c>
     </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>215</v>
       </c>
@@ -18031,7 +18046,7 @@
         <v>2235835.7755</v>
       </c>
     </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>215</v>
       </c>
@@ -18093,7 +18108,7 @@
         <v>20307.625</v>
       </c>
     </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>215</v>
       </c>
@@ -18155,7 +18170,7 @@
         <v>31420</v>
       </c>
     </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
         <v>215</v>
       </c>
@@ -18217,7 +18232,7 @@
         <v>439780.16499999998</v>
       </c>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>215</v>
       </c>
@@ -18279,7 +18294,7 @@
         <v>121493.875</v>
       </c>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>215</v>
       </c>
@@ -18341,7 +18356,7 @@
         <v>212393.1925</v>
       </c>
     </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>215</v>
       </c>
@@ -18403,7 +18418,7 @@
         <v>81676.802500000005</v>
       </c>
     </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>215</v>
       </c>
@@ -18465,7 +18480,7 @@
         <v>59304.077499999999</v>
       </c>
     </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>215</v>
       </c>
@@ -18527,7 +18542,7 @@
         <v>2024255.1274999999</v>
       </c>
     </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
         <v>215</v>
       </c>
@@ -18589,7 +18604,7 @@
         <v>7280575.0575000001</v>
       </c>
     </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
         <v>215</v>
       </c>
@@ -18651,7 +18666,7 @@
         <v>607.5</v>
       </c>
     </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>215</v>
       </c>
@@ -18713,7 +18728,7 @@
         <v>1012.5</v>
       </c>
     </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>215</v>
       </c>
@@ -18775,7 +18790,7 @@
         <v>28362.49</v>
       </c>
     </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>215</v>
       </c>
@@ -18837,7 +18852,7 @@
         <v>26675</v>
       </c>
     </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>215</v>
       </c>
@@ -18899,7 +18914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>215</v>
       </c>
@@ -18961,7 +18976,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>215</v>
       </c>
@@ -19023,7 +19038,7 @@
         <v>2961.09</v>
       </c>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
         <v>215</v>
       </c>
@@ -19085,7 +19100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>215</v>
       </c>
@@ -19147,7 +19162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
         <v>215</v>
       </c>
@@ -19209,7 +19224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>215</v>
       </c>
@@ -19271,7 +19286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>215</v>
       </c>
@@ -19333,7 +19348,7 @@
         <v>1635.1075000000001</v>
       </c>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>215</v>
       </c>
@@ -19395,7 +19410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
         <v>215</v>
       </c>
@@ -19457,7 +19472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
         <v>215</v>
       </c>
@@ -19519,7 +19534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
         <v>215</v>
       </c>
@@ -19581,7 +19596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
         <v>215</v>
       </c>
@@ -19643,7 +19658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
         <v>215</v>
       </c>
@@ -19705,7 +19720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
         <v>215</v>
       </c>
@@ -19767,7 +19782,7 @@
         <v>28.975000000000001</v>
       </c>
     </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
         <v>215</v>
       </c>
@@ -19829,7 +19844,7 @@
         <v>42357.0075</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
         <v>215</v>
       </c>
@@ -19891,7 +19906,7 @@
         <v>2397.5</v>
       </c>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
         <v>215</v>
       </c>
@@ -19953,7 +19968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
         <v>215</v>
       </c>
@@ -20015,7 +20030,7 @@
         <v>180520.54</v>
       </c>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
         <v>215</v>
       </c>
@@ -20077,7 +20092,7 @@
         <v>263398.40500000003</v>
       </c>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
         <v>215</v>
       </c>
@@ -20139,7 +20154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
         <v>215</v>
       </c>
@@ -20201,7 +20216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
         <v>215</v>
       </c>
@@ -20263,7 +20278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
         <v>215</v>
       </c>
@@ -20325,7 +20340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
         <v>215</v>
       </c>
@@ -20387,7 +20402,7 @@
         <v>81268.535000000003</v>
       </c>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
         <v>215</v>
       </c>
@@ -20449,7 +20464,7 @@
         <v>2048387.0375000001</v>
       </c>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
         <v>215</v>
       </c>
@@ -20511,7 +20526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
         <v>378</v>
       </c>
@@ -20573,7 +20588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
         <v>378</v>
       </c>
@@ -20635,7 +20650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
         <v>378</v>
       </c>
@@ -20697,7 +20712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
         <v>378</v>
       </c>
@@ -20759,7 +20774,7 @@
         <v>29312.5</v>
       </c>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
         <v>378</v>
       </c>
@@ -20821,7 +20836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
         <v>378</v>
       </c>
@@ -20883,7 +20898,7 @@
         <v>68676.3</v>
       </c>
     </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
         <v>378</v>
       </c>
@@ -20945,7 +20960,7 @@
         <v>612677.58499999996</v>
       </c>
     </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
         <v>378</v>
       </c>
@@ -21007,7 +21022,7 @@
         <v>21892.27</v>
       </c>
     </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
         <v>378</v>
       </c>
@@ -21069,7 +21084,7 @@
         <v>11665.28</v>
       </c>
     </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
         <v>378</v>
       </c>
@@ -21131,7 +21146,7 @@
         <v>598073.75</v>
       </c>
     </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
         <v>378</v>
       </c>
@@ -21193,7 +21208,7 @@
         <v>153562.5</v>
       </c>
     </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
         <v>378</v>
       </c>
@@ -21255,7 +21270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
         <v>378</v>
       </c>
@@ -21317,7 +21332,7 @@
         <v>10125</v>
       </c>
     </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
         <v>378</v>
       </c>
@@ -21379,7 +21394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
         <v>378</v>
       </c>
@@ -21441,7 +21456,7 @@
         <v>578137.31499999994</v>
       </c>
     </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
         <v>378</v>
       </c>
@@ -21503,7 +21518,7 @@
         <v>380802.65250000003</v>
       </c>
     </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
         <v>378</v>
       </c>
@@ -21565,7 +21580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
         <v>378</v>
       </c>
@@ -21627,7 +21642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
         <v>378</v>
       </c>
@@ -21689,7 +21704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
         <v>378</v>
       </c>
@@ -21751,7 +21766,7 @@
         <v>4264214.1425000001</v>
       </c>
     </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
         <v>378</v>
       </c>
@@ -21813,7 +21828,7 @@
         <v>3535148.5150000001</v>
       </c>
     </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
         <v>378</v>
       </c>
@@ -21875,7 +21890,7 @@
         <v>113702.56</v>
       </c>
     </row>
-    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
         <v>378</v>
       </c>
@@ -21937,7 +21952,7 @@
         <v>2303953.15</v>
       </c>
     </row>
-    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
         <v>378</v>
       </c>
@@ -21999,7 +22014,7 @@
         <v>24746.924999999999</v>
       </c>
     </row>
-    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
         <v>378</v>
       </c>
@@ -22061,7 +22076,7 @@
         <v>155108.57750000001</v>
       </c>
     </row>
-    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
         <v>378</v>
       </c>
@@ -22123,7 +22138,7 @@
         <v>701816.12250000006</v>
       </c>
     </row>
-    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
         <v>378</v>
       </c>
@@ -22185,7 +22200,7 @@
         <v>118211.825</v>
       </c>
     </row>
-    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
         <v>378</v>
       </c>
@@ -22247,7 +22262,7 @@
         <v>453956.065</v>
       </c>
     </row>
-    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
         <v>378</v>
       </c>
@@ -22309,7 +22324,7 @@
         <v>2780.5475000000001</v>
       </c>
     </row>
-    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
         <v>378</v>
       </c>
@@ -22371,7 +22386,7 @@
         <v>2132704.0924999998</v>
       </c>
     </row>
-    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
         <v>378</v>
       </c>
@@ -22433,7 +22448,7 @@
         <v>40853.245000000003</v>
       </c>
     </row>
-    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
         <v>378</v>
       </c>
@@ -22495,7 +22510,7 @@
         <v>3648098.9525000001</v>
       </c>
     </row>
-    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
         <v>378</v>
       </c>
@@ -22557,7 +22572,7 @@
         <v>2620794.5150000001</v>
       </c>
     </row>
-    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
         <v>378</v>
       </c>
@@ -22619,7 +22634,7 @@
         <v>855371.51</v>
       </c>
     </row>
-    <row r="334" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
         <v>378</v>
       </c>
@@ -22681,7 +22696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
         <v>378</v>
       </c>
@@ -22743,7 +22758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
         <v>378</v>
       </c>
@@ -22805,7 +22820,7 @@
         <v>31789.5</v>
       </c>
     </row>
-    <row r="337" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>378</v>
       </c>
@@ -22867,7 +22882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
         <v>378</v>
       </c>
@@ -22929,7 +22944,7 @@
         <v>1177.04</v>
       </c>
     </row>
-    <row r="339" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
         <v>378</v>
       </c>
@@ -22991,7 +23006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
         <v>378</v>
       </c>
@@ -23053,7 +23068,7 @@
         <v>23317.327499999999</v>
       </c>
     </row>
-    <row r="341" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
         <v>378</v>
       </c>
@@ -23115,7 +23130,7 @@
         <v>10201267.6175</v>
       </c>
     </row>
-    <row r="342" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
         <v>378</v>
       </c>
@@ -23177,7 +23192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
         <v>378</v>
       </c>
@@ -23239,7 +23254,7 @@
         <v>22370909.112500001</v>
       </c>
     </row>
-    <row r="344" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
         <v>378</v>
       </c>
@@ -23301,7 +23316,7 @@
         <v>1071005.7075</v>
       </c>
     </row>
-    <row r="345" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
         <v>378</v>
       </c>
@@ -23363,7 +23378,7 @@
         <v>4288524.1475</v>
       </c>
     </row>
-    <row r="346" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
         <v>378</v>
       </c>
@@ -23425,7 +23440,7 @@
         <v>25259105.232500002</v>
       </c>
     </row>
-    <row r="347" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
         <v>378</v>
       </c>
@@ -23487,7 +23502,7 @@
         <v>13871760.237500001</v>
       </c>
     </row>
-    <row r="348" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
         <v>378</v>
       </c>
@@ -23549,7 +23564,7 @@
         <v>155260.17499999999</v>
       </c>
     </row>
-    <row r="349" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
         <v>378</v>
       </c>
@@ -23611,7 +23626,7 @@
         <v>1529045.3525</v>
       </c>
     </row>
-    <row r="350" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
         <v>378</v>
       </c>
@@ -23673,7 +23688,7 @@
         <v>23449663.802499998</v>
       </c>
     </row>
-    <row r="351" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
         <v>378</v>
       </c>
@@ -23735,7 +23750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
         <v>378</v>
       </c>
@@ -23797,7 +23812,7 @@
         <v>12041.254999999999</v>
       </c>
     </row>
-    <row r="353" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
         <v>378</v>
       </c>
@@ -23859,7 +23874,7 @@
         <v>578276.33250000002</v>
       </c>
     </row>
-    <row r="354" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
         <v>378</v>
       </c>
@@ -23921,7 +23936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
         <v>378</v>
       </c>
@@ -23983,7 +23998,7 @@
         <v>7095704.5274999999</v>
       </c>
     </row>
-    <row r="356" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
         <v>378</v>
       </c>
@@ -24045,7 +24060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
         <v>378</v>
       </c>
@@ -24107,7 +24122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
         <v>378</v>
       </c>
@@ -24169,7 +24184,7 @@
         <v>490527.0675</v>
       </c>
     </row>
-    <row r="359" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
         <v>378</v>
       </c>
@@ -24231,7 +24246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
         <v>378</v>
       </c>
@@ -24293,7 +24308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
         <v>378</v>
       </c>
@@ -24355,7 +24370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
         <v>378</v>
       </c>
@@ -24417,7 +24432,7 @@
         <v>10431815.067500001</v>
       </c>
     </row>
-    <row r="363" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
         <v>378</v>
       </c>
@@ -24479,7 +24494,7 @@
         <v>97798.927500000005</v>
       </c>
     </row>
-    <row r="364" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
         <v>378</v>
       </c>
@@ -24541,7 +24556,7 @@
         <v>63570323.5625</v>
       </c>
     </row>
-    <row r="365" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
         <v>378</v>
       </c>
@@ -24603,7 +24618,7 @@
         <v>2725673.91</v>
       </c>
     </row>
-    <row r="366" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
         <v>378</v>
       </c>
@@ -24665,7 +24680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
         <v>378</v>
       </c>
@@ -24727,7 +24742,7 @@
         <v>8607.1224999999995</v>
       </c>
     </row>
-    <row r="368" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
         <v>378</v>
       </c>
@@ -24789,7 +24804,7 @@
         <v>25462.8825</v>
       </c>
     </row>
-    <row r="369" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
         <v>378</v>
       </c>
@@ -24851,7 +24866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
         <v>378</v>
       </c>
@@ -24913,7 +24928,7 @@
         <v>3609973.0375000001</v>
       </c>
     </row>
-    <row r="371" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
         <v>378</v>
       </c>
@@ -24975,7 +24990,7 @@
         <v>24285083.9575</v>
       </c>
     </row>
-    <row r="372" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
         <v>378</v>
       </c>
@@ -25037,7 +25052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
         <v>378</v>
       </c>
@@ -25099,7 +25114,7 @@
         <v>170996868.62</v>
       </c>
     </row>
-    <row r="374" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
         <v>378</v>
       </c>
@@ -25161,7 +25176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
         <v>378</v>
       </c>
@@ -25223,7 +25238,7 @@
         <v>846872.1</v>
       </c>
     </row>
-    <row r="376" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
         <v>378</v>
       </c>
@@ -25285,7 +25300,7 @@
         <v>13672128.7325</v>
       </c>
     </row>
-    <row r="377" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
         <v>378</v>
       </c>
@@ -25347,7 +25362,7 @@
         <v>9326445.9774999991</v>
       </c>
     </row>
-    <row r="378" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="s">
         <v>378</v>
       </c>
@@ -25409,7 +25424,7 @@
         <v>33394070.899999999</v>
       </c>
     </row>
-    <row r="379" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="s">
         <v>378</v>
       </c>
@@ -25471,7 +25486,7 @@
         <v>945546.29249999998</v>
       </c>
     </row>
-    <row r="380" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
         <v>378</v>
       </c>
@@ -25533,7 +25548,7 @@
         <v>210659.33249999999</v>
       </c>
     </row>
-    <row r="381" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
         <v>378</v>
       </c>
@@ -25595,7 +25610,7 @@
         <v>429149.20500000002</v>
       </c>
     </row>
-    <row r="382" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
         <v>378</v>
       </c>
@@ -25657,7 +25672,7 @@
         <v>1744193.2775000001</v>
       </c>
     </row>
-    <row r="383" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="s">
         <v>378</v>
       </c>
@@ -25719,7 +25734,7 @@
         <v>1587776.615</v>
       </c>
     </row>
-    <row r="384" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="s">
         <v>378</v>
       </c>
@@ -25781,7 +25796,7 @@
         <v>1226895.2849999999</v>
       </c>
     </row>
-    <row r="385" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
         <v>378</v>
       </c>
@@ -25843,7 +25858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
         <v>378</v>
       </c>
@@ -25905,7 +25920,7 @@
         <v>2041390.8025</v>
       </c>
     </row>
-    <row r="387" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
         <v>378</v>
       </c>
@@ -25967,7 +25982,7 @@
         <v>73104721.209999993</v>
       </c>
     </row>
-    <row r="388" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
         <v>378</v>
       </c>
@@ -26029,7 +26044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
         <v>378</v>
       </c>
@@ -26091,7 +26106,7 @@
         <v>4275764.9474999998</v>
       </c>
     </row>
-    <row r="390" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
         <v>378</v>
       </c>
@@ -26153,7 +26168,7 @@
         <v>12101298.484999999</v>
       </c>
     </row>
-    <row r="391" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
         <v>378</v>
       </c>
@@ -26215,7 +26230,7 @@
         <v>2374886.415</v>
       </c>
     </row>
-    <row r="392" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
         <v>378</v>
       </c>
@@ -26277,7 +26292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
         <v>378</v>
       </c>
@@ -26339,7 +26354,7 @@
         <v>3262873.5175000001</v>
       </c>
     </row>
-    <row r="394" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
         <v>378</v>
       </c>
@@ -26401,7 +26416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
         <v>378</v>
       </c>
@@ -26463,7 +26478,7 @@
         <v>490758.10499999998</v>
       </c>
     </row>
-    <row r="396" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
         <v>378</v>
       </c>
@@ -26525,7 +26540,7 @@
         <v>22358451.375</v>
       </c>
     </row>
-    <row r="397" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
         <v>378</v>
       </c>
@@ -26587,7 +26602,7 @@
         <v>239012630.88</v>
       </c>
     </row>
-    <row r="398" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
         <v>378</v>
       </c>
@@ -26649,7 +26664,7 @@
         <v>7449876.3049999997</v>
       </c>
     </row>
-    <row r="399" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
         <v>378</v>
       </c>
@@ -26711,7 +26726,7 @@
         <v>62479344.482500002</v>
       </c>
     </row>
-    <row r="400" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
         <v>378</v>
       </c>
@@ -26773,7 +26788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
         <v>378</v>
       </c>
@@ -26835,7 +26850,7 @@
         <v>2680714.3774999999</v>
       </c>
     </row>
-    <row r="402" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
         <v>378</v>
       </c>
@@ -26897,7 +26912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
         <v>378</v>
       </c>
@@ -26959,7 +26974,7 @@
         <v>39579.682500000003</v>
       </c>
     </row>
-    <row r="404" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
         <v>378</v>
       </c>
@@ -27021,7 +27036,7 @@
         <v>352014.60749999998</v>
       </c>
     </row>
-    <row r="405" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
         <v>378</v>
       </c>
@@ -27083,7 +27098,7 @@
         <v>2386076.5874999999</v>
       </c>
     </row>
-    <row r="406" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
         <v>378</v>
       </c>
@@ -27145,7 +27160,7 @@
         <v>1744611.37</v>
       </c>
     </row>
-    <row r="407" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
         <v>378</v>
       </c>
@@ -27207,7 +27222,7 @@
         <v>1732430.7424999999</v>
       </c>
     </row>
-    <row r="408" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
         <v>378</v>
       </c>
@@ -27269,7 +27284,7 @@
         <v>652938.21750000003</v>
       </c>
     </row>
-    <row r="409" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A409" s="4"/>
       <c r="B409" s="4"/>
       <c r="C409" s="4"/>
@@ -27286,22 +27301,10 @@
       <c r="N409" s="4"/>
       <c r="O409" s="4"/>
       <c r="P409" s="4"/>
-      <c r="Q409" s="5">
-        <f>SUM(Q3:Q408)</f>
-        <v>3253265044</v>
-      </c>
-      <c r="R409" s="5">
-        <f t="shared" ref="R409:T409" si="0">SUM(R3:R408)</f>
-        <v>2862346652.7779975</v>
-      </c>
-      <c r="S409" s="5">
-        <f t="shared" si="0"/>
-        <v>2684373950.8579984</v>
-      </c>
-      <c r="T409" s="5">
-        <f t="shared" si="0"/>
-        <v>2666982817.0249987</v>
-      </c>
+      <c r="Q409" s="5"/>
+      <c r="R409" s="5"/>
+      <c r="S409" s="5"/>
+      <c r="T409" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
